--- a/revisao_pandas/base_tratada_alunos.xlsx
+++ b/revisao_pandas/base_tratada_alunos.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
